--- a/artfynd/A 47977-2024 artfynd.xlsx
+++ b/artfynd/A 47977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112183461</v>
+        <v>112183931</v>
       </c>
       <c r="B2" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667004</v>
+        <v>667301</v>
       </c>
       <c r="R2" t="n">
-        <v>7185304</v>
+        <v>7185258</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112182633</v>
+        <v>112183672</v>
       </c>
       <c r="B3" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666976</v>
+        <v>666970</v>
       </c>
       <c r="R3" t="n">
-        <v>7185314</v>
+        <v>7185255</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,19 +887,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112183672</v>
+        <v>112183673</v>
       </c>
       <c r="B4" t="n">
-        <v>90869</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666970</v>
+        <v>667065</v>
       </c>
       <c r="R4" t="n">
-        <v>7185255</v>
+        <v>7185346</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112182563</v>
+        <v>112183674</v>
       </c>
       <c r="B5" t="n">
-        <v>77441</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667069</v>
+        <v>667240</v>
       </c>
       <c r="R5" t="n">
-        <v>7185356</v>
+        <v>7185211</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,16 +1102,11 @@
         <v>112183676</v>
       </c>
       <c r="B6" t="n">
-        <v>90869</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112182635</v>
+        <v>112183677</v>
       </c>
       <c r="B7" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667022</v>
+        <v>667241</v>
       </c>
       <c r="R7" t="n">
-        <v>7185310</v>
+        <v>7185354</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,6 +1308,1490 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112183461</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>667004</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7185304</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112183462</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>667230</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7185352</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112182633</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>666976</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7185314</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112182635</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>667022</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7185311</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112182637</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>667269</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7185319</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112182640</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>667231</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7185350</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112182185</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>667218</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7185301</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112182799</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>667162</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7185254</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112182801</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>667220</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7185227</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112182803</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>667294</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7185299</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112182805</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>667239</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7185350</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112182563</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>667069</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7185356</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112183338</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>667230</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7185209</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>112181878</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>667051</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7185364</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47977-2024 artfynd.xlsx
+++ b/artfynd/A 47977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183674</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183677</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183461</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183462</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182633</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182635</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182637</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182640</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182185</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182799</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182803</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182805</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182563</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183338</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,8 +2892,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181878</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>